--- a/docs/Template_PRJ301_AI_Usage_Report_Template (1) (2).xlsx
+++ b/docs/Template_PRJ301_AI_Usage_Report_Template (1) (2).xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\PRJ---24-7-LLM-Tutor\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA4EE475-E647-4BB2-AD96-A73EA683F87C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A63AE5EC-EC2A-4E0E-A3AD-CC44ED98BCCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0.Overview" sheetId="1" r:id="rId1"/>
     <sheet name="1. Week 1" sheetId="2" r:id="rId2"/>
     <sheet name="1. Week 2" sheetId="5" r:id="rId3"/>
-    <sheet name="2. Week n" sheetId="3" r:id="rId4"/>
+    <sheet name="Week 4" sheetId="3" r:id="rId4"/>
     <sheet name="Instruction" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="181029"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="140">
   <si>
     <t>PRJ301 - Project AI Usage Report</t>
   </si>
@@ -274,52 +274,6 @@
   </si>
   <si>
     <t>The AI structure may not fully fit our project scope. Checked and adjusted package naming before project setup.</t>
-  </si>
-  <si>
-    <t>&lt;&lt;sample data&gt;&gt;
-Implementation</t>
-  </si>
-  <si>
-    <t>Servlet + JSP CRUD for Assignment module</t>
-  </si>
-  <si>
-    <t>GitHub Copilot</t>
-  </si>
-  <si>
-    <t>Generated AssignmentServlet doGet/doPost skeleton</t>
-  </si>
-  <si>
-    <t>Fixed SQL injection risk, added PreparedStatement</t>
-  </si>
-  <si>
-    <t>GitHub commit link</t>
-  </si>
-  <si>
-    <t>1 Servlet, 4 JSP pages, 6 methods</t>
-  </si>
-  <si>
-    <t>Generated code used string concatenation for SQL</t>
-  </si>
-  <si>
-    <t>Testing</t>
-  </si>
-  <si>
-    <t>Test case generation for login &amp; submission upload</t>
-  </si>
-  <si>
-    <t>12 draft test cases (positive/negative)</t>
-  </si>
-  <si>
-    <t>Kept 9, removed 3 irrelevant to Servlet routing</t>
-  </si>
-  <si>
-    <t>Google Sheet link</t>
-  </si>
-  <si>
-    <t>9 test cases, 7 passed</t>
-  </si>
-  <si>
-    <t>Missed edge case for expired deadline</t>
   </si>
   <si>
     <t>Column</t>
@@ -418,13 +372,447 @@
   </si>
   <si>
     <t>AI initially suggested relationships and attributes that did not fully match the project's Use Cases. Manual review was required to correct cardinalities, foreign keys, and unnecessary data.</t>
+  </si>
+  <si>
+    <t>Connect database with Java code using JDBC</t>
+  </si>
+  <si>
+    <t>1 working DBContext class</t>
+  </si>
+  <si>
+    <t>AI suggested a generic connection string; had to manually adjust port and database credentials to match local environment.</t>
+  </si>
+  <si>
+    <r>
+      <t>Provided the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>DBContext.java</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> class with the correct JDBC connection string and driver setup for SQL Server.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Verified the connection string, adjusted the database name to </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>AITA_DB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>, and added the MS SQL JDBC driver to the project library.</t>
+    </r>
+  </si>
+  <si>
+    <t>Connect web pages with Java code using Servlet</t>
+  </si>
+  <si>
+    <t>5 main Servlets mapped to JSPs</t>
+  </si>
+  <si>
+    <t>Implement full CRUD operations for the project</t>
+  </si>
+  <si>
+    <t>Checked for SQL injection vulnerabilities, validated parameterized queries, and integrated DAO methods with corresponding Servlets.</t>
+  </si>
+  <si>
+    <t>1 complete DAO class with 5 CRUD operations</t>
+  </si>
+  <si>
+    <t>Add Expression Language (EL) and Servlet Filter</t>
+  </si>
+  <si>
+    <t>1 Filter class and 2 updated JSP files</t>
+  </si>
+  <si>
+    <t>AI Filter logic sometimes redirected incorrectly; manually fixed the logic to prevent infinite redirect loops.</t>
+  </si>
+  <si>
+    <t>Testing &amp; Implementation</t>
+  </si>
+  <si>
+    <t>Add exception paths and error handling</t>
+  </si>
+  <si>
+    <t>Tested edge cases by inputting invalid role IDs and duplicate emails, verified that the app returned user-friendly error messages.</t>
+  </si>
+  <si>
+    <t>Handled 3 major exception scenarios</t>
+  </si>
+  <si>
+    <t>AI's error messages were in English; manually translated them to Vietnamese to match the system's language requirement.</t>
+  </si>
+  <si>
+    <r>
+      <t>Generated standard Servlet structure (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>doGet</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>doPost</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>) and explained </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>@WebServlet</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> routing for mapping JSP files.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Reviewed the Servlet code, customized the URL patterns (e.g., </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>/login</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>/user</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>), and ensured requests forward correctly to the views.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>AI used deprecated imports (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>javax.servlet</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> instead of </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>jakarta.servlet</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>); manually corrected imports to match Tomcat 10.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Wrote SQL queries using </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>PreparedStatement</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> and provided full CRUD logic (Create, Read, Update, Delete) in </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>UserDAO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>AI code lacked specific error handling for foreign key constraints; manually added </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>catch</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> blocks for SQL Error 547.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Provided </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>AuthFilter.java</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> for route protection and showed how to replace standard Java code in JSP with EL (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>${...}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Applied the Filter to sensitive routes (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>/user</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>/add</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>/update</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>), and refactored </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>login.jsp</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> to use EL for displaying error messages.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Suggested </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>try-catch</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> implementations for data conversion (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>NumberFormatException</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>) and DB duplicates (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>SQLException</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> 2627).</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -487,6 +875,22 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9.9"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -503,12 +907,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFD9E1F2"/>
         <bgColor rgb="FFD9E1F2"/>
       </patternFill>
@@ -519,8 +917,14 @@
         <bgColor rgb="FFE2EFDA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -567,6 +971,19 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB7B7B7"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB7B7B7"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB7B7B7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -574,7 +991,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -588,12 +1005,6 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -609,13 +1020,13 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -633,11 +1044,20 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -645,17 +1065,17 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -968,99 +1388,99 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="28.05" customHeight="1">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="20" t="s">
+      <c r="B4" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="21"/>
-      <c r="D4" s="21"/>
-      <c r="E4" s="21"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="20" t="s">
+      <c r="B5" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="21"/>
-      <c r="D5" s="21"/>
-      <c r="E5" s="21"/>
+      <c r="C5" s="22"/>
+      <c r="D5" s="22"/>
+      <c r="E5" s="22"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="20" t="s">
+      <c r="B6" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="21"/>
-      <c r="D6" s="21"/>
-      <c r="E6" s="21"/>
+      <c r="C6" s="22"/>
+      <c r="D6" s="22"/>
+      <c r="E6" s="22"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="20" t="s">
+      <c r="B7" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="21"/>
-      <c r="D7" s="21"/>
-      <c r="E7" s="21"/>
+      <c r="C7" s="22"/>
+      <c r="D7" s="22"/>
+      <c r="E7" s="22"/>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="20">
+      <c r="B8" s="21">
         <v>4</v>
       </c>
-      <c r="C8" s="21"/>
-      <c r="D8" s="21"/>
-      <c r="E8" s="21"/>
+      <c r="C8" s="22"/>
+      <c r="D8" s="22"/>
+      <c r="E8" s="22"/>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="12" t="s">
+      <c r="A9" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="20" t="s">
+      <c r="B9" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="21"/>
-      <c r="D9" s="21"/>
-      <c r="E9" s="21"/>
+      <c r="C9" s="22"/>
+      <c r="D9" s="22"/>
+      <c r="E9" s="22"/>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="22" t="s">
+      <c r="A11" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="23"/>
-      <c r="C11" s="23"/>
-      <c r="D11" s="23"/>
-      <c r="E11" s="24"/>
+      <c r="B11" s="24"/>
+      <c r="C11" s="24"/>
+      <c r="D11" s="24"/>
+      <c r="E11" s="25"/>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="4" t="s">
@@ -1080,87 +1500,87 @@
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="14">
+      <c r="A13" s="12">
         <v>1</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C13" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="D13" s="13" t="s">
+      <c r="D13" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="E13" s="13" t="s">
+      <c r="E13" s="11" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="14">
+      <c r="A14" s="12">
         <v>2</v>
       </c>
-      <c r="B14" s="13" t="s">
+      <c r="B14" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="C14" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="D14" s="13" t="s">
+      <c r="D14" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="E14" s="13" t="s">
+      <c r="E14" s="11" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="26.4">
-      <c r="A15" s="14">
+      <c r="A15" s="12">
         <v>3</v>
       </c>
-      <c r="B15" s="13" t="s">
+      <c r="B15" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="C15" s="13" t="s">
+      <c r="C15" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="D15" s="13" t="s">
+      <c r="D15" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="E15" s="13" t="s">
+      <c r="E15" s="11" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="14">
+      <c r="A16" s="12">
         <v>4</v>
       </c>
-      <c r="B16" s="13" t="s">
+      <c r="B16" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="C16" s="13" t="s">
+      <c r="C16" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="D16" s="13" t="s">
+      <c r="D16" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="E16" s="13" t="s">
+      <c r="E16" s="11" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="14">
+      <c r="A17" s="12">
         <v>5</v>
       </c>
-      <c r="B17" s="13" t="s">
+      <c r="B17" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="C17" s="13" t="s">
+      <c r="C17" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="D17" s="13" t="s">
+      <c r="D17" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="E17" s="13" t="s">
+      <c r="E17" s="11" t="s">
         <v>33</v>
       </c>
     </row>
@@ -1230,98 +1650,98 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="96" customHeight="1">
-      <c r="A2" s="7">
+      <c r="A2" s="5">
         <v>1</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="G2" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="I2" s="8">
+      <c r="I2" s="6">
         <v>5</v>
       </c>
-      <c r="J2" s="8" t="s">
+      <c r="J2" s="6" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="108" customHeight="1">
-      <c r="A3" s="7">
+      <c r="A3" s="5">
         <v>2</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="G3" s="10" t="s">
+      <c r="G3" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="H3" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="I3" s="7">
+      <c r="I3" s="5">
         <v>4</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="J3" s="6" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="115.2">
-      <c r="A4" s="7">
+      <c r="A4" s="5">
         <v>3</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="H4" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="I4" s="7">
+      <c r="I4" s="5">
         <v>4</v>
       </c>
-      <c r="J4" s="8" t="s">
+      <c r="J4" s="6" t="s">
         <v>68</v>
       </c>
     </row>
@@ -1385,163 +1805,163 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="121.05" customHeight="1">
-      <c r="A2" s="7">
+      <c r="A2" s="5">
         <v>1</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="G2" s="11" t="s">
+      <c r="G2" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="I2" s="8">
+      <c r="I2" s="6">
         <v>5</v>
       </c>
-      <c r="J2" s="8" t="s">
+      <c r="J2" s="6" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="142.94999999999999" customHeight="1">
-      <c r="A3" s="7">
+      <c r="A3" s="5">
         <v>2</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="E3" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="I3" s="5">
+        <v>5</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="139.05000000000001" customHeight="1">
+      <c r="A4" s="5">
+        <v>3</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="I4" s="5">
+        <v>4</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="201.6">
+      <c r="A5" s="5">
+        <v>4</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="F5" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="G5" s="17" t="s">
+        <v>107</v>
+      </c>
+      <c r="H5" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="I5" s="6">
+        <v>4</v>
+      </c>
+      <c r="J5" s="15" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="144">
+      <c r="A6" s="5">
+        <v>5</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="D6" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="E6" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="F6" s="19" t="s">
         <v>110</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="G6" s="20" t="s">
         <v>111</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="H6" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="F3" s="15" t="s">
+      <c r="I6" s="6">
+        <v>5</v>
+      </c>
+      <c r="J6" s="7" t="s">
         <v>113</v>
-      </c>
-      <c r="G3" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="H3" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="I3" s="7">
-        <v>5</v>
-      </c>
-      <c r="J3" s="8" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="139.05000000000001" customHeight="1">
-      <c r="A4" s="7">
-        <v>3</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="D4" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="G4" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="H4" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="I4" s="7">
-        <v>4</v>
-      </c>
-      <c r="J4" s="8" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="201.6">
-      <c r="A5" s="7">
-        <v>4</v>
-      </c>
-      <c r="B5" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="C5" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="D5" s="18" t="s">
-        <v>63</v>
-      </c>
-      <c r="E5" s="17" t="s">
-        <v>118</v>
-      </c>
-      <c r="F5" s="17" t="s">
-        <v>119</v>
-      </c>
-      <c r="G5" s="19" t="s">
-        <v>122</v>
-      </c>
-      <c r="H5" s="17" t="s">
-        <v>120</v>
-      </c>
-      <c r="I5" s="8">
-        <v>4</v>
-      </c>
-      <c r="J5" s="17" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="144">
-      <c r="A6" s="26">
-        <v>5</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="D6" s="27" t="s">
-        <v>76</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="F6" s="28" t="s">
-        <v>125</v>
-      </c>
-      <c r="G6" s="29" t="s">
-        <v>126</v>
-      </c>
-      <c r="H6" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="I6" s="8">
-        <v>5</v>
-      </c>
-      <c r="J6" s="9" t="s">
-        <v>128</v>
       </c>
     </row>
   </sheetData>
@@ -1558,7 +1978,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -1577,96 +1997,182 @@
       <c r="A1" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="28" t="s">
         <v>40</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="28" t="s">
         <v>41</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="28" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="39.6">
-      <c r="A2" s="5">
+    <row r="2" spans="1:10" ht="47.4">
+      <c r="A2" s="27">
         <v>1</v>
       </c>
-      <c r="B2" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="I2" s="5">
+      <c r="B2" s="29" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2" s="30" t="s">
+        <v>114</v>
+      </c>
+      <c r="D2" s="30" t="s">
+        <v>48</v>
+      </c>
+      <c r="E2" s="30" t="s">
+        <v>117</v>
+      </c>
+      <c r="F2" s="30" t="s">
+        <v>118</v>
+      </c>
+      <c r="G2" s="30"/>
+      <c r="H2" s="30" t="s">
+        <v>115</v>
+      </c>
+      <c r="I2" s="30">
         <v>5</v>
       </c>
-      <c r="J2" s="6" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="26.4">
-      <c r="A3" s="5">
+      <c r="J2" s="30" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="60.6">
+      <c r="A3" s="6">
         <v>2</v>
       </c>
-      <c r="B3" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="I3" s="5">
+      <c r="B3" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C3" s="30" t="s">
+        <v>119</v>
+      </c>
+      <c r="D3" s="30" t="s">
+        <v>48</v>
+      </c>
+      <c r="E3" s="30" t="s">
+        <v>132</v>
+      </c>
+      <c r="F3" s="30" t="s">
+        <v>133</v>
+      </c>
+      <c r="G3" s="30"/>
+      <c r="H3" s="30" t="s">
+        <v>120</v>
+      </c>
+      <c r="I3" s="30">
+        <v>4</v>
+      </c>
+      <c r="J3" s="30" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="49.2">
+      <c r="A4" s="6">
         <v>3</v>
       </c>
-      <c r="J3" s="6" t="s">
-        <v>96</v>
+      <c r="B4" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C4" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="D4" s="30" t="s">
+        <v>48</v>
+      </c>
+      <c r="E4" s="30" t="s">
+        <v>135</v>
+      </c>
+      <c r="F4" s="30" t="s">
+        <v>122</v>
+      </c>
+      <c r="G4" s="30"/>
+      <c r="H4" s="30" t="s">
+        <v>123</v>
+      </c>
+      <c r="I4" s="30">
+        <v>5</v>
+      </c>
+      <c r="J4" s="30" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="49.2">
+      <c r="A5" s="6">
+        <v>4</v>
+      </c>
+      <c r="B5" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" s="30" t="s">
+        <v>124</v>
+      </c>
+      <c r="D5" s="30" t="s">
+        <v>48</v>
+      </c>
+      <c r="E5" s="30" t="s">
+        <v>137</v>
+      </c>
+      <c r="F5" s="30" t="s">
+        <v>138</v>
+      </c>
+      <c r="G5" s="30"/>
+      <c r="H5" s="30" t="s">
+        <v>125</v>
+      </c>
+      <c r="I5" s="30">
+        <v>4</v>
+      </c>
+      <c r="J5" s="30" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="75.599999999999994">
+      <c r="A6" s="6">
+        <v>5</v>
+      </c>
+      <c r="B6" s="30" t="s">
+        <v>127</v>
+      </c>
+      <c r="C6" s="30" t="s">
+        <v>128</v>
+      </c>
+      <c r="D6" s="30" t="s">
+        <v>48</v>
+      </c>
+      <c r="E6" s="30" t="s">
+        <v>139</v>
+      </c>
+      <c r="F6" s="30" t="s">
+        <v>129</v>
+      </c>
+      <c r="G6" s="30"/>
+      <c r="H6" s="30" t="s">
+        <v>130</v>
+      </c>
+      <c r="I6" s="30">
+        <v>5</v>
+      </c>
+      <c r="J6" s="30" t="s">
+        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -1685,10 +2191,10 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -1696,7 +2202,7 @@
         <v>36</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="26.4">
@@ -1704,7 +2210,7 @@
         <v>37</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="26.4">
@@ -1712,7 +2218,7 @@
         <v>38</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1720,7 +2226,7 @@
         <v>39</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="26.4">
@@ -1728,7 +2234,7 @@
         <v>40</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="26.4">
@@ -1736,7 +2242,7 @@
         <v>41</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="39.6">
@@ -1744,7 +2250,7 @@
         <v>42</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>105</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="26.4">
@@ -1752,7 +2258,7 @@
         <v>43</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1760,7 +2266,7 @@
         <v>44</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="26.4">
@@ -1768,7 +2274,7 @@
         <v>45</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>108</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Template_PRJ301_AI_Usage_Report_Template (1) (2).xlsx
+++ b/docs/Template_PRJ301_AI_Usage_Report_Template (1) (2).xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\PRJ---24-7-LLM-Tutor\docs\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A63AE5EC-EC2A-4E0E-A3AD-CC44ED98BCCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="21876" windowHeight="9840" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="0.Overview" sheetId="1" r:id="rId1"/>
@@ -19,12 +13,25 @@
     <sheet name="Week 4" sheetId="3" r:id="rId4"/>
     <sheet name="Instruction" sheetId="4" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="147">
   <si>
     <t>PRJ301 - Project AI Usage Report</t>
   </si>
@@ -255,6 +262,30 @@
     <t>AI initially missed exception paths and suggested dangerous SQL constraints (CASCADE). Iterative prompting and manual corrections were required to meet academic standards.</t>
   </si>
   <si>
+    <t>System Design &amp; Implementation</t>
+  </si>
+  <si>
+    <t>Designing System Screen Flow Diagram (Draw.io) &amp; Constructing User Interface (UX/UI Design System &amp; SPA Layout)</t>
+  </si>
+  <si>
+    <t>Claude 3.5 / Antigravity / ChatGPT-4o</t>
+  </si>
+  <si>
+    <t>Role-based Navigation Screen Flow in Untitled Diagram.drawio (Student/Lecturer) and HTML/CSS/JS Dark Mode Glassmorphism UI code for 5 system view panels.</t>
+  </si>
+  <si>
+    <t>Added bidirectional navigation edges and role-differentiated color coding on Draw.io; refactored CSS Flexbox/Grid layouts, implemented smooth transitions, and fixed responsive overflow bugs on the Session History table.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1TsNLKc7zhuCoEUPjxf-lhVzScFA5SqKi?usp=sharing</t>
+  </si>
+  <si>
+    <t>Saved 70% of design time (~4.5 hours), delivered 100% complete interactive Screen Flow and responsive UI.</t>
+  </si>
+  <si>
+    <t>AI initially suggested overly complex UX flows, generated CSS with responsive overflow issues on smaller viewports, and lacked proper color contrast.</t>
+  </si>
+  <si>
     <t>Design MVC architecture and package structure for the 24/7 LLM Tutor module</t>
   </si>
   <si>
@@ -274,6 +305,497 @@
   </si>
   <si>
     <t>The AI structure may not fully fit our project scope. Checked and adjusted package naming before project setup.</t>
+  </si>
+  <si>
+    <t>Design Use Case Diagram and 8 Use Case Specifications for the 24/7 LLM Tutor.</t>
+  </si>
+  <si>
+    <t>Generated the Use Case Diagram with 3 actors (Admin, Instructor, Student) and 8 use cases: UC01 Login &amp; Authorization, UC02 Manage User List, UC03 Manage Assignments, UC04 Submit ZIP &amp; SHA-256 Hashing, UC05 View Scores &amp; Feedback, UC06 Detect Error &amp; Initialize AI Session, UC07 Interact with 24/7 AI Tutor, and UC08 Get Personalized Learning Path. Generated detailed descriptions including main flows and exceptions for all 8 use cases.</t>
+  </si>
+  <si>
+    <t>Reviewed the generated use cases against the project requirements. Modified actor–use case relationships, use case names, main flows, and exception flows to match the AITA 24/7 LLM Tutor project.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1_IiKnUxj3SQwrN2uhQHVUB0enmRgof_9?usp=sharing</t>
+  </si>
+  <si>
+    <t>3 actors, 8 use cases, 11 actor–use case associations, 8 detailed use case specifications</t>
+  </si>
+  <si>
+    <t>Some AI-generated use case relationships and descriptions may not fully match the project requirements and therefore required manual review and modification.</t>
+  </si>
+  <si>
+    <t>Design Domain Model and ERD for the 24/7 LLM Tutor module</t>
+  </si>
+  <si>
+    <t>Generated a Domain Model and ERD structure for the core learning features, including Student, TutorConversation, TutorMessage, CodeError, LearningRecommendation, and LearningTopic, with suggested PK/FK relationships and cardinalities.</t>
+  </si>
+  <si>
+    <t>Compared the AI-generated model with the project Use Cases and requirements. Corrected entity responsibilities, PK/FK mapping, relationship cardinalities, and removed unnecessary attributes. Reviewed the model for 3NF consistency before preparing domain-model.md, erd.md, and README.md.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1Cv8UVkfH270j3_3KHpU-v4wu6AA63oxH?hl=vi</t>
+  </si>
+  <si>
+    <t>6 core entities; PK/FK and cardinalities defined; 3 documentation files prepared</t>
+  </si>
+  <si>
+    <t>AI initially suggested relationships and attributes that did not fully match the project's Use Cases. Manual review was required to correct cardinalities, foreign keys, and unnecessary data.</t>
+  </si>
+  <si>
+    <t>Connect database with Java code using JDBC</t>
+  </si>
+  <si>
+    <t>Gemini, Chatgpt, Copilot</t>
+  </si>
+  <si>
+    <r>
+      <t>Provided the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>DBContext.java</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t> class with the correct JDBC connection string and driver setup for SQL Server.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Verified the connection string, adjusted the database name to </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>AITA_DB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>, and added the MS SQL JDBC driver to the project library.</t>
+    </r>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1Al2zQH-_4wk5DT_6O8csILsFFIXu45rO?usp=sharing</t>
+  </si>
+  <si>
+    <t>1 working DBContext class</t>
+  </si>
+  <si>
+    <t>AI suggested a generic connection string; had to manually adjust port and database credentials to match local environment.</t>
+  </si>
+  <si>
+    <t>Connect web pages with Java code using Servlet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gemini, Chatgpt, </t>
+  </si>
+  <si>
+    <r>
+      <t>Generated standard Servlet structure (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>doGet</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>doPost</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>) and explained </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>@WebServlet</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t> routing for mapping JSP files.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Reviewed the Servlet code, customized the URL patterns (e.g., </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>/login</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>/user</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>), and ensured requests forward correctly to the views.</t>
+    </r>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1mkeoPv7QBeEjPVionr3T6jgvSR-VMuW3?usp=sharing</t>
+  </si>
+  <si>
+    <t>5 main Servlets mapped to JSPs</t>
+  </si>
+  <si>
+    <r>
+      <t>AI used deprecated imports (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>javax.servlet</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t> instead of </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>jakarta.servlet</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>); manually corrected imports to match Tomcat 10.</t>
+    </r>
+  </si>
+  <si>
+    <t>Implement full CRUD operations for the project</t>
+  </si>
+  <si>
+    <t>Gemini, Claue</t>
+  </si>
+  <si>
+    <r>
+      <t>Wrote SQL queries using </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PreparedStatement</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t> and provided full CRUD logic (Create, Read, Update, Delete) in </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>UserDAO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Checked for SQL injection vulnerabilities, validated parameterized queries, and integrated DAO methods with corresponding Servlets.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1BT8UQCi9wl8cJyHOPO71V5_QBshXmKtW?usp=sharing</t>
+  </si>
+  <si>
+    <t>1 complete DAO class with 5 CRUD operations</t>
+  </si>
+  <si>
+    <r>
+      <t>AI code lacked specific error handling for foreign key constraints; manually added </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>catch</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t> blocks for SQL Error 547.</t>
+    </r>
+  </si>
+  <si>
+    <t>Add Expression Language (EL) and Servlet Filter</t>
+  </si>
+  <si>
+    <r>
+      <t>Provided </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>AuthFilter.java</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t> for route protection and showed how to replace standard Java code in JSP with EL (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>${...}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Applied the Filter to sensitive routes (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>/user</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>/add</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>/update</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>), and refactored </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>login.jsp</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t> to use EL for displaying error messages.</t>
+    </r>
+  </si>
+  <si>
+    <t>1 Filter class and 2 updated JSP files</t>
+  </si>
+  <si>
+    <t>AI Filter logic sometimes redirected incorrectly; manually fixed the logic to prevent infinite redirect loops.</t>
+  </si>
+  <si>
+    <t>Testing &amp; Implementation</t>
+  </si>
+  <si>
+    <t>Add exception paths and error handling</t>
+  </si>
+  <si>
+    <r>
+      <t>Suggested </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>try-catch</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t> implementations for data conversion (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>NumberFormatException</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>) and DB duplicates (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>SQLException</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t> 2627).</t>
+    </r>
+  </si>
+  <si>
+    <t>Tested edge cases by inputting invalid role IDs and duplicate emails, verified that the app returned user-friendly error messages.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/18528q5unPQgaTq-89bPzC0Es6qiiTV2f?usp=sharing</t>
+  </si>
+  <si>
+    <t>Handled 3 major exception scenarios</t>
+  </si>
+  <si>
+    <t>AI's error messages were in English; manually translated them to Vietnamese to match the system's language requirement.</t>
   </si>
   <si>
     <t>Column</t>
@@ -312,507 +834,19 @@
   </si>
   <si>
     <t>What limitations or risks you observed when using AI (e.g., “generated SQL injection-prone code”, “missing validation logic”, “incomplete test coverage”).</t>
-  </si>
-  <si>
-    <t>System Design &amp; Implementation</t>
-  </si>
-  <si>
-    <t>Designing System Screen Flow Diagram (Draw.io) &amp; Constructing User Interface (UX/UI Design System &amp; SPA Layout)</t>
-  </si>
-  <si>
-    <t>Claude 3.5 / Antigravity / ChatGPT-4o</t>
-  </si>
-  <si>
-    <t>Role-based Navigation Screen Flow in Untitled Diagram.drawio (Student/Lecturer) and HTML/CSS/JS Dark Mode Glassmorphism UI code for 5 system view panels.</t>
-  </si>
-  <si>
-    <t>Added bidirectional navigation edges and role-differentiated color coding on Draw.io; refactored CSS Flexbox/Grid layouts, implemented smooth transitions, and fixed responsive overflow bugs on the Session History table.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/drive/folders/1TsNLKc7zhuCoEUPjxf-lhVzScFA5SqKi?usp=sharing</t>
-  </si>
-  <si>
-    <t>Saved 70% of design time (~4.5 hours), delivered 100% complete interactive Screen Flow and responsive UI.</t>
-  </si>
-  <si>
-    <t>AI initially suggested overly complex UX flows, generated CSS with responsive overflow issues on smaller viewports, and lacked proper color contrast.</t>
-  </si>
-  <si>
-    <t>Design Use Case Diagram and 8 Use Case Specifications for the 24/7 LLM Tutor.</t>
-  </si>
-  <si>
-    <t>Generated the Use Case Diagram with 3 actors (Admin, Instructor, Student) and 8 use cases: UC01 Login &amp; Authorization, UC02 Manage User List, UC03 Manage Assignments, UC04 Submit ZIP &amp; SHA-256 Hashing, UC05 View Scores &amp; Feedback, UC06 Detect Error &amp; Initialize AI Session, UC07 Interact with 24/7 AI Tutor, and UC08 Get Personalized Learning Path. Generated detailed descriptions including main flows and exceptions for all 8 use cases.</t>
-  </si>
-  <si>
-    <t>Reviewed the generated use cases against the project requirements. Modified actor–use case relationships, use case names, main flows, and exception flows to match the AITA 24/7 LLM Tutor project.</t>
-  </si>
-  <si>
-    <t>3 actors, 8 use cases, 11 actor–use case associations, 8 detailed use case specifications</t>
-  </si>
-  <si>
-    <t>Some AI-generated use case relationships and descriptions may not fully match the project requirements and therefore required manual review and modification.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/drive/folders/1_IiKnUxj3SQwrN2uhQHVUB0enmRgof_9?usp=sharing</t>
-  </si>
-  <si>
-    <t>Design Domain Model and ERD for the 24/7 LLM Tutor module</t>
-  </si>
-  <si>
-    <t>Generated a Domain Model and ERD structure for the core learning features, including Student, TutorConversation, TutorMessage, CodeError, LearningRecommendation, and LearningTopic, with suggested PK/FK relationships and cardinalities.</t>
-  </si>
-  <si>
-    <t>Compared the AI-generated model with the project Use Cases and requirements. Corrected entity responsibilities, PK/FK mapping, relationship cardinalities, and removed unnecessary attributes. Reviewed the model for 3NF consistency before preparing domain-model.md, erd.md, and README.md.</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/drive/folders/1Cv8UVkfH270j3_3KHpU-v4wu6AA63oxH?hl=vi</t>
-  </si>
-  <si>
-    <t>6 core entities; PK/FK and cardinalities defined; 3 documentation files prepared</t>
-  </si>
-  <si>
-    <t>AI initially suggested relationships and attributes that did not fully match the project's Use Cases. Manual review was required to correct cardinalities, foreign keys, and unnecessary data.</t>
-  </si>
-  <si>
-    <t>Connect database with Java code using JDBC</t>
-  </si>
-  <si>
-    <t>1 working DBContext class</t>
-  </si>
-  <si>
-    <t>AI suggested a generic connection string; had to manually adjust port and database credentials to match local environment.</t>
-  </si>
-  <si>
-    <r>
-      <t>Provided the </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.9"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>DBContext.java</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t> class with the correct JDBC connection string and driver setup for SQL Server.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Verified the connection string, adjusted the database name to </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.9"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>AITA_DB</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>, and added the MS SQL JDBC driver to the project library.</t>
-    </r>
-  </si>
-  <si>
-    <t>Connect web pages with Java code using Servlet</t>
-  </si>
-  <si>
-    <t>5 main Servlets mapped to JSPs</t>
-  </si>
-  <si>
-    <t>Implement full CRUD operations for the project</t>
-  </si>
-  <si>
-    <t>Checked for SQL injection vulnerabilities, validated parameterized queries, and integrated DAO methods with corresponding Servlets.</t>
-  </si>
-  <si>
-    <t>1 complete DAO class with 5 CRUD operations</t>
-  </si>
-  <si>
-    <t>Add Expression Language (EL) and Servlet Filter</t>
-  </si>
-  <si>
-    <t>1 Filter class and 2 updated JSP files</t>
-  </si>
-  <si>
-    <t>AI Filter logic sometimes redirected incorrectly; manually fixed the logic to prevent infinite redirect loops.</t>
-  </si>
-  <si>
-    <t>Testing &amp; Implementation</t>
-  </si>
-  <si>
-    <t>Add exception paths and error handling</t>
-  </si>
-  <si>
-    <t>Tested edge cases by inputting invalid role IDs and duplicate emails, verified that the app returned user-friendly error messages.</t>
-  </si>
-  <si>
-    <t>Handled 3 major exception scenarios</t>
-  </si>
-  <si>
-    <t>AI's error messages were in English; manually translated them to Vietnamese to match the system's language requirement.</t>
-  </si>
-  <si>
-    <r>
-      <t>Generated standard Servlet structure (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.9"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>doGet</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.9"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>doPost</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>) and explained </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.9"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>@WebServlet</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t> routing for mapping JSP files.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Reviewed the Servlet code, customized the URL patterns (e.g., </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.9"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>/login</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.9"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>/user</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>), and ensured requests forward correctly to the views.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>AI used deprecated imports (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.9"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>javax.servlet</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t> instead of </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.9"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>jakarta.servlet</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>); manually corrected imports to match Tomcat 10.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Wrote SQL queries using </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.9"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>PreparedStatement</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t> and provided full CRUD logic (Create, Read, Update, Delete) in </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.9"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>UserDAO</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>AI code lacked specific error handling for foreign key constraints; manually added </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.9"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>catch</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t> blocks for SQL Error 547.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Provided </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.9"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>AuthFilter.java</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t> for route protection and showed how to replace standard Java code in JSP with EL (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.9"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>${...}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>).</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Applied the Filter to sensitive routes (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.9"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>/user</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.9"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>/add</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.9"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>/update</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>), and refactored </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.9"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>login.jsp</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t> to use EL for displaying error messages.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Suggested </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.9"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>try-catch</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t> implementations for data conversion (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.9"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>NumberFormatException</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>) and DB duplicates (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.9"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>SQLException</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t> 2627).</t>
-    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-* #,##0.00\ &quot;₫&quot;_-;\-* #,##0.00\ &quot;₫&quot;_-;_-* &quot;-&quot;??\ &quot;₫&quot;_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_-* #,##0\ &quot;₫&quot;_-;\-* #,##0\ &quot;₫&quot;_-;_-* &quot;-&quot;\ &quot;₫&quot;_-;_-@_-"/>
+  </numFmts>
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -821,51 +855,62 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -873,26 +918,151 @@
       <sz val="14"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
-      <sz val="8"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9.9"/>
-      <name val="Consolas"/>
-      <family val="3"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -907,6 +1077,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFD9E1F2"/>
         <bgColor rgb="FFD9E1F2"/>
       </patternFill>
@@ -919,12 +1095,192 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -945,6 +1301,19 @@
       <bottom style="thin">
         <color rgb="FFB7B7B7"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB7B7B7"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB7B7B7"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB7B7B7"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -973,36 +1342,280 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFB7B7B7"/>
+        <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
-        <color rgb="FFB7B7B7"/>
+        <color rgb="FFB2B2B2"/>
       </right>
       <top style="thin">
-        <color rgb="FFB7B7B7"/>
+        <color rgb="FFB2B2B2"/>
       </top>
-      <bottom/>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1014,34 +1627,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="6" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="6" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1050,46 +1651,82 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="6" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1374,113 +2011,88 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:E17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="5" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="28.05" customHeight="1">
-      <c r="A1" s="26" t="s">
+    <row r="1" ht="28.05" customHeight="1" spans="1:5">
+      <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="22"/>
-      <c r="D3" s="22"/>
-      <c r="E3" s="22"/>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="21" t="s">
+      <c r="B4" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="22"/>
-      <c r="D5" s="22"/>
-      <c r="E5" s="22"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="10" t="s">
+      <c r="A6" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="21" t="s">
+      <c r="B6" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="22"/>
-      <c r="D6" s="22"/>
-      <c r="E6" s="22"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="21" t="s">
+      <c r="B7" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="22"/>
-      <c r="D7" s="22"/>
-      <c r="E7" s="22"/>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="10" t="s">
+      <c r="A8" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="21">
+      <c r="B8" s="26">
         <v>4</v>
       </c>
-      <c r="C8" s="22"/>
-      <c r="D8" s="22"/>
-      <c r="E8" s="22"/>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="21" t="s">
+      <c r="B9" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="22"/>
-      <c r="D9" s="22"/>
-      <c r="E9" s="22"/>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="23" t="s">
+      <c r="A11" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="24"/>
-      <c r="C11" s="24"/>
-      <c r="D11" s="24"/>
-      <c r="E11" s="25"/>
+      <c r="B11" s="27"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="28"/>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="4" t="s">
@@ -1500,110 +2112,112 @@
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="12">
+      <c r="A13" s="29">
         <v>1</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="B13" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="D13" s="11" t="s">
+      <c r="D13" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="E13" s="11" t="s">
+      <c r="E13" s="26" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="12">
+      <c r="A14" s="29">
         <v>2</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B14" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C14" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="D14" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="E14" s="11" t="s">
+      <c r="E14" s="26" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="26.4">
-      <c r="A15" s="12">
+    <row r="15" ht="26.4" spans="1:5">
+      <c r="A15" s="29">
         <v>3</v>
       </c>
-      <c r="B15" s="11" t="s">
+      <c r="B15" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="C15" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="D15" s="11" t="s">
+      <c r="D15" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="E15" s="11" t="s">
+      <c r="E15" s="26" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="12">
+      <c r="A16" s="29">
         <v>4</v>
       </c>
-      <c r="B16" s="11" t="s">
+      <c r="B16" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="C16" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="D16" s="11" t="s">
+      <c r="D16" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="E16" s="11" t="s">
+      <c r="E16" s="26" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="12">
+      <c r="A17" s="29">
         <v>5</v>
       </c>
-      <c r="B17" s="11" t="s">
+      <c r="B17" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="C17" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="D17" s="11" t="s">
+      <c r="D17" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="E17" s="11" t="s">
+      <c r="E17" s="26" t="s">
         <v>33</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="B9:E9"/>
-    <mergeCell ref="A11:E11"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="B4:E4"/>
     <mergeCell ref="B5:E5"/>
     <mergeCell ref="B6:E6"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="A11:E11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:J4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="3"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -1617,7 +2231,7 @@
     <col min="10" max="10" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="30" customHeight="1">
+    <row r="1" ht="30" customHeight="1" spans="1:10">
       <c r="A1" s="4" t="s">
         <v>36</v>
       </c>
@@ -1649,122 +2263,124 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="96" customHeight="1">
-      <c r="A2" s="5">
+    <row r="2" ht="96" customHeight="1" spans="1:10">
+      <c r="A2" s="11">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="G2" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="I2" s="6">
+      <c r="I2" s="12">
         <v>5</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="J2" s="12" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="108" customHeight="1">
-      <c r="A3" s="5">
+    <row r="3" ht="108" customHeight="1" spans="1:10">
+      <c r="A3" s="11">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="23" t="s">
         <v>58</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="I3" s="5">
+      <c r="I3" s="11">
         <v>4</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="J3" s="12" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="115.2">
-      <c r="A4" s="5">
+    <row r="4" ht="115.2" spans="1:10">
+      <c r="A4" s="11">
         <v>3</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="G4" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="H4" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="I4" s="5">
+      <c r="I4" s="11">
         <v>4</v>
       </c>
-      <c r="J4" s="6" t="s">
+      <c r="J4" s="12" t="s">
         <v>68</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="G2" r:id="rId1" tooltip="https://drive.google.com/drive/folders/1oCtqgnVtzyzi2f7mUUQB_5rVcpYybpqx?usp=drive_link" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
-    <hyperlink ref="G3" r:id="rId2" tooltip="https://drive.google.com/drive/folders/1mpiZZy8ocuyEM1UMS9VQfdk0BRl87rm_?usp=sharing" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
-    <hyperlink ref="G4" r:id="rId3" xr:uid="{00000000-0004-0000-0100-000002000000}"/>
+    <hyperlink ref="G2" r:id="rId1" display="https://drive.google.com/drive/folders/1oCtqgnVtzyzi2f7mUUQB_5rVcpYybpqx?usp=drive_link" tooltip="https://drive.google.com/drive/folders/1oCtqgnVtzyzi2f7mUUQB_5rVcpYybpqx?usp=drive_link"/>
+    <hyperlink ref="G3" r:id="rId2" display="https://drive.google.com/drive/folders/1mpiZZy8ocuyEM1UMS9VQfdk0BRl87rm_?usp=sharing" tooltip="https://drive.google.com/drive/folders/1mpiZZy8ocuyEM1UMS9VQfdk0BRl87rm_?usp=sharing"/>
+    <hyperlink ref="G4" r:id="rId3" display="https://drive.google.com/drive/folders/1hkfM8Mek8vMbZPqjB3AijcdotsKPLGua?usp=sharing"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:J6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="5"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="38.33203125" customWidth="1"/>
-    <col min="4" max="4" width="15.5546875" customWidth="1"/>
-    <col min="5" max="5" width="31.44140625" customWidth="1"/>
+    <col min="3" max="3" width="38.3333333333333" customWidth="1"/>
+    <col min="4" max="4" width="15.5555555555556" customWidth="1"/>
+    <col min="5" max="5" width="31.4444444444444" customWidth="1"/>
     <col min="6" max="6" width="30" customWidth="1"/>
     <col min="7" max="7" width="18" customWidth="1"/>
     <col min="8" max="8" width="20" customWidth="1"/>
@@ -1772,7 +2388,7 @@
     <col min="10" max="10" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="30" customHeight="1">
+    <row r="1" ht="30" customHeight="1" spans="1:10">
       <c r="A1" s="4" t="s">
         <v>36</v>
       </c>
@@ -1804,182 +2420,184 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="121.05" customHeight="1">
-      <c r="A2" s="5">
+    <row r="2" ht="121.05" customHeight="1" spans="1:10">
+      <c r="A2" s="11">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="G2" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="I2" s="6">
+      <c r="I2" s="12">
         <v>5</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="J2" s="12" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="142.94999999999999" customHeight="1">
-      <c r="A3" s="5">
+    <row r="3" ht="142.95" customHeight="1" spans="1:10">
+      <c r="A3" s="11">
         <v>2</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="G3" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="H3" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="I3" s="11">
+        <v>5</v>
+      </c>
+      <c r="J3" s="12" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="4" ht="139.05" customHeight="1" spans="1:10">
+      <c r="A4" s="11">
+        <v>3</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="G4" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="H4" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="I4" s="11">
+        <v>4</v>
+      </c>
+      <c r="J4" s="12" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="5" ht="187.2" spans="1:10">
+      <c r="A5" s="11">
+        <v>4</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="D5" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="E5" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="F5" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="G5" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="H5" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="I5" s="12">
+        <v>4</v>
+      </c>
+      <c r="J5" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="D3" s="13" t="s">
+    </row>
+    <row r="6" ht="144" spans="1:10">
+      <c r="A6" s="11">
+        <v>5</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="D6" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="E6" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="F6" s="21" t="s">
         <v>98</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="G6" s="22" t="s">
         <v>99</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H6" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="I3" s="5">
+      <c r="I6" s="12">
         <v>5</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="J6" s="13" t="s">
         <v>101</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="139.05000000000001" customHeight="1">
-      <c r="A4" s="5">
-        <v>3</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="D4" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="I4" s="5">
-        <v>4</v>
-      </c>
-      <c r="J4" s="6" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="201.6">
-      <c r="A5" s="5">
-        <v>4</v>
-      </c>
-      <c r="B5" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="C5" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="D5" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="E5" s="15" t="s">
-        <v>103</v>
-      </c>
-      <c r="F5" s="15" t="s">
-        <v>104</v>
-      </c>
-      <c r="G5" s="17" t="s">
-        <v>107</v>
-      </c>
-      <c r="H5" s="15" t="s">
-        <v>105</v>
-      </c>
-      <c r="I5" s="6">
-        <v>4</v>
-      </c>
-      <c r="J5" s="15" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="144">
-      <c r="A6" s="5">
-        <v>5</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="D6" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="F6" s="19" t="s">
-        <v>110</v>
-      </c>
-      <c r="G6" s="20" t="s">
-        <v>111</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="I6" s="6">
-        <v>5</v>
-      </c>
-      <c r="J6" s="7" t="s">
-        <v>113</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="G4" r:id="rId1" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
-    <hyperlink ref="G3" r:id="rId2" xr:uid="{88FF8E4D-AB20-4BD2-8574-82AFE88F9E13}"/>
-    <hyperlink ref="G2" r:id="rId3" xr:uid="{501F067C-697C-4220-A862-1205015787E2}"/>
-    <hyperlink ref="G5" r:id="rId4" xr:uid="{54149B39-3898-44D3-B264-6816775C6CC8}"/>
-    <hyperlink ref="G6" r:id="rId5" xr:uid="{0587752F-533C-4EAB-B92A-01C112087A94}"/>
+    <hyperlink ref="G4" r:id="rId1" display="https://drive.google.com/drive/folders/1jfv8FE53NmF0-9jNc803u7VXSKQBN8MB?usp=sharing"/>
+    <hyperlink ref="G3" r:id="rId2" display="https://drive.google.com/drive/folders/1TsNLKc7zhuCoEUPjxf-lhVzScFA5SqKi?usp=sharing"/>
+    <hyperlink ref="G2" r:id="rId3" display="https://drive.google.com/drive/folders/1MvIEKYq72RDwufT_sIZ_XiyqlYSTz0PZ?usp=sharing"/>
+    <hyperlink ref="G5" r:id="rId4" display="https://drive.google.com/drive/folders/1_IiKnUxj3SQwrN2uhQHVUB0enmRgof_9?usp=sharing"/>
+    <hyperlink ref="G6" r:id="rId5" display="https://drive.google.com/drive/folders/1Cv8UVkfH270j3_3KHpU-v4wu6AA63oxH?hl=vi"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:J6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="5"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -1993,197 +2611,213 @@
     <col min="10" max="10" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="30" customHeight="1">
+    <row r="1" ht="30" customHeight="1" spans="1:10">
       <c r="A1" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="28" t="s">
+      <c r="B1" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C1" s="28" t="s">
+      <c r="C1" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="28" t="s">
+      <c r="D1" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="28" t="s">
+      <c r="E1" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="F1" s="28" t="s">
+      <c r="F1" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="G1" s="28" t="s">
+      <c r="G1" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="H1" s="28" t="s">
+      <c r="H1" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="I1" s="28" t="s">
+      <c r="I1" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="J1" s="28" t="s">
+      <c r="J1" s="5" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="47.4">
-      <c r="A2" s="27">
+    <row r="2" ht="86.4" spans="1:10">
+      <c r="A2" s="6">
         <v>1</v>
       </c>
-      <c r="B2" s="29" t="s">
+      <c r="B2" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="C2" s="30" t="s">
+      <c r="C2" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="I2" s="8">
+        <v>5</v>
+      </c>
+      <c r="J2" s="8" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="3" ht="72" spans="1:10">
+      <c r="A3" s="10">
+        <v>2</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="H3" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="D2" s="30" t="s">
-        <v>48</v>
-      </c>
-      <c r="E2" s="30" t="s">
+      <c r="I3" s="8">
+        <v>4</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="4" ht="72" spans="1:10">
+      <c r="A4" s="10">
+        <v>3</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="D4" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="F2" s="30" t="s">
+      <c r="E4" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="G2" s="30"/>
-      <c r="H2" s="30" t="s">
-        <v>115</v>
-      </c>
-      <c r="I2" s="30">
+      <c r="F4" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="I4" s="8">
         <v>5</v>
       </c>
-      <c r="J2" s="30" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="60.6">
-      <c r="A3" s="6">
-        <v>2</v>
-      </c>
-      <c r="B3" s="30" t="s">
+      <c r="J4" s="8" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="5" ht="55.2" spans="1:10">
+      <c r="A5" s="10">
+        <v>4</v>
+      </c>
+      <c r="B5" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="C3" s="30" t="s">
-        <v>119</v>
-      </c>
-      <c r="D3" s="30" t="s">
-        <v>48</v>
-      </c>
-      <c r="E3" s="30" t="s">
+      <c r="C5" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="I5" s="8">
+        <v>4</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="6" ht="82.8" spans="1:10">
+      <c r="A6" s="10">
+        <v>5</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="G6" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="F3" s="30" t="s">
+      <c r="H6" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="G3" s="30"/>
-      <c r="H3" s="30" t="s">
-        <v>120</v>
-      </c>
-      <c r="I3" s="30">
-        <v>4</v>
-      </c>
-      <c r="J3" s="30" t="s">
+      <c r="I6" s="8">
+        <v>5</v>
+      </c>
+      <c r="J6" s="8" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="49.2">
-      <c r="A4" s="6">
-        <v>3</v>
-      </c>
-      <c r="B4" s="30" t="s">
-        <v>54</v>
-      </c>
-      <c r="C4" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="D4" s="30" t="s">
-        <v>48</v>
-      </c>
-      <c r="E4" s="30" t="s">
-        <v>135</v>
-      </c>
-      <c r="F4" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="G4" s="30"/>
-      <c r="H4" s="30" t="s">
-        <v>123</v>
-      </c>
-      <c r="I4" s="30">
-        <v>5</v>
-      </c>
-      <c r="J4" s="30" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="49.2">
-      <c r="A5" s="6">
-        <v>4</v>
-      </c>
-      <c r="B5" s="30" t="s">
-        <v>54</v>
-      </c>
-      <c r="C5" s="30" t="s">
-        <v>124</v>
-      </c>
-      <c r="D5" s="30" t="s">
-        <v>48</v>
-      </c>
-      <c r="E5" s="30" t="s">
-        <v>137</v>
-      </c>
-      <c r="F5" s="30" t="s">
-        <v>138</v>
-      </c>
-      <c r="G5" s="30"/>
-      <c r="H5" s="30" t="s">
-        <v>125</v>
-      </c>
-      <c r="I5" s="30">
-        <v>4</v>
-      </c>
-      <c r="J5" s="30" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="75.599999999999994">
-      <c r="A6" s="6">
-        <v>5</v>
-      </c>
-      <c r="B6" s="30" t="s">
-        <v>127</v>
-      </c>
-      <c r="C6" s="30" t="s">
-        <v>128</v>
-      </c>
-      <c r="D6" s="30" t="s">
-        <v>48</v>
-      </c>
-      <c r="E6" s="30" t="s">
-        <v>139</v>
-      </c>
-      <c r="F6" s="30" t="s">
-        <v>129</v>
-      </c>
-      <c r="G6" s="30"/>
-      <c r="H6" s="30" t="s">
-        <v>130</v>
-      </c>
-      <c r="I6" s="30">
-        <v>5</v>
-      </c>
-      <c r="J6" s="30" t="s">
-        <v>131</v>
-      </c>
-    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="G2" r:id="rId1" display="https://drive.google.com/drive/folders/1Al2zQH-_4wk5DT_6O8csILsFFIXu45rO?usp=sharing"/>
+    <hyperlink ref="G3" r:id="rId2" display="https://drive.google.com/drive/folders/1mkeoPv7QBeEjPVionr3T6jgvSR-VMuW3?usp=sharing"/>
+    <hyperlink ref="G6" r:id="rId3" display="https://drive.google.com/drive/folders/18528q5unPQgaTq-89bPzC0Es6qiiTV2f?usp=sharing"/>
+    <hyperlink ref="G4" r:id="rId4" display="https://drive.google.com/drive/folders/1BT8UQCi9wl8cJyHOPO71V5_QBshXmKtW?usp=sharing"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
     <col min="2" max="2" width="90" customWidth="1"/>
@@ -2191,10 +2825,10 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>82</v>
+        <v>135</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>83</v>
+        <v>136</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -2202,23 +2836,23 @@
         <v>36</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="26.4">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="3" ht="26.4" spans="1:2">
       <c r="A3" s="2" t="s">
         <v>37</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="26.4">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="4" ht="26.4" spans="1:2">
       <c r="A4" s="2" t="s">
         <v>38</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>86</v>
+        <v>139</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -2226,39 +2860,39 @@
         <v>39</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="26.4">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="6" ht="26.4" spans="1:2">
       <c r="A6" s="2" t="s">
         <v>40</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="26.4">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="7" ht="26.4" spans="1:2">
       <c r="A7" s="2" t="s">
         <v>41</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="39.6">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="8" ht="39.6" spans="1:2">
       <c r="A8" s="2" t="s">
         <v>42</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="26.4">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="9" ht="26.4" spans="1:2">
       <c r="A9" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>91</v>
+        <v>144</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -2266,18 +2900,19 @@
         <v>44</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="26.4">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="11" ht="26.4" spans="1:2">
       <c r="A11" s="2" t="s">
         <v>45</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>93</v>
+        <v>146</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/docs/Template_PRJ301_AI_Usage_Report_Template (1) (2).xlsx
+++ b/docs/Template_PRJ301_AI_Usage_Report_Template (1) (2).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\PRJ---24-7-LLM-Tutor\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A63AE5EC-EC2A-4E0E-A3AD-CC44ED98BCCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A6BC8CB-809B-4CD1-9363-DA2E296AD326}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="141">
   <si>
     <t>PRJ301 - Project AI Usage Report</t>
   </si>
@@ -806,6 +806,9 @@
       </rPr>
       <t> 2627).</t>
     </r>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1HDAnlKy5GQiDcsJ5ka-zU_YZRkGuqeTY?usp=sharing</t>
   </si>
 </sst>
 </file>
@@ -991,7 +994,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1052,6 +1055,18 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1065,16 +1080,7 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1388,99 +1394,99 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="28.05" customHeight="1">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="22"/>
-      <c r="D3" s="22"/>
-      <c r="E3" s="22"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="21" t="s">
+      <c r="B4" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26"/>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="22"/>
-      <c r="D5" s="22"/>
-      <c r="E5" s="22"/>
+      <c r="C5" s="26"/>
+      <c r="D5" s="26"/>
+      <c r="E5" s="26"/>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="21" t="s">
+      <c r="B6" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="22"/>
-      <c r="D6" s="22"/>
-      <c r="E6" s="22"/>
+      <c r="C6" s="26"/>
+      <c r="D6" s="26"/>
+      <c r="E6" s="26"/>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="21" t="s">
+      <c r="B7" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="22"/>
-      <c r="D7" s="22"/>
-      <c r="E7" s="22"/>
+      <c r="C7" s="26"/>
+      <c r="D7" s="26"/>
+      <c r="E7" s="26"/>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="21">
+      <c r="B8" s="25">
         <v>4</v>
       </c>
-      <c r="C8" s="22"/>
-      <c r="D8" s="22"/>
-      <c r="E8" s="22"/>
+      <c r="C8" s="26"/>
+      <c r="D8" s="26"/>
+      <c r="E8" s="26"/>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="21" t="s">
+      <c r="B9" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="22"/>
-      <c r="D9" s="22"/>
-      <c r="E9" s="22"/>
+      <c r="C9" s="26"/>
+      <c r="D9" s="26"/>
+      <c r="E9" s="26"/>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="23" t="s">
+      <c r="A11" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="24"/>
-      <c r="C11" s="24"/>
-      <c r="D11" s="24"/>
-      <c r="E11" s="25"/>
+      <c r="B11" s="28"/>
+      <c r="C11" s="28"/>
+      <c r="D11" s="28"/>
+      <c r="E11" s="29"/>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="4" t="s">
@@ -1997,61 +2003,61 @@
       <c r="A1" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="28" t="s">
+      <c r="B1" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="C1" s="28" t="s">
+      <c r="C1" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="28" t="s">
+      <c r="D1" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="28" t="s">
+      <c r="E1" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="F1" s="28" t="s">
+      <c r="F1" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="G1" s="28" t="s">
+      <c r="G1" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="H1" s="28" t="s">
+      <c r="H1" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="I1" s="28" t="s">
+      <c r="I1" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="J1" s="28" t="s">
+      <c r="J1" s="22" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="47.4">
-      <c r="A2" s="27">
+      <c r="A2" s="21">
         <v>1</v>
       </c>
-      <c r="B2" s="29" t="s">
+      <c r="B2" s="23" t="s">
         <v>54</v>
       </c>
-      <c r="C2" s="30" t="s">
+      <c r="C2" s="24" t="s">
         <v>114</v>
       </c>
-      <c r="D2" s="30" t="s">
+      <c r="D2" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="E2" s="30" t="s">
+      <c r="E2" s="24" t="s">
         <v>117</v>
       </c>
-      <c r="F2" s="30" t="s">
+      <c r="F2" s="24" t="s">
         <v>118</v>
       </c>
-      <c r="G2" s="30"/>
-      <c r="H2" s="30" t="s">
+      <c r="G2" s="24"/>
+      <c r="H2" s="24" t="s">
         <v>115</v>
       </c>
-      <c r="I2" s="30">
+      <c r="I2" s="24">
         <v>5</v>
       </c>
-      <c r="J2" s="30" t="s">
+      <c r="J2" s="24" t="s">
         <v>116</v>
       </c>
     </row>
@@ -2059,29 +2065,29 @@
       <c r="A3" s="6">
         <v>2</v>
       </c>
-      <c r="B3" s="30" t="s">
+      <c r="B3" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="C3" s="30" t="s">
+      <c r="C3" s="24" t="s">
         <v>119</v>
       </c>
-      <c r="D3" s="30" t="s">
+      <c r="D3" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="E3" s="30" t="s">
+      <c r="E3" s="24" t="s">
         <v>132</v>
       </c>
-      <c r="F3" s="30" t="s">
+      <c r="F3" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="G3" s="30"/>
-      <c r="H3" s="30" t="s">
+      <c r="G3" s="24"/>
+      <c r="H3" s="24" t="s">
         <v>120</v>
       </c>
-      <c r="I3" s="30">
+      <c r="I3" s="24">
         <v>4</v>
       </c>
-      <c r="J3" s="30" t="s">
+      <c r="J3" s="24" t="s">
         <v>134</v>
       </c>
     </row>
@@ -2089,59 +2095,61 @@
       <c r="A4" s="6">
         <v>3</v>
       </c>
-      <c r="B4" s="30" t="s">
+      <c r="B4" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="C4" s="30" t="s">
+      <c r="C4" s="24" t="s">
         <v>121</v>
       </c>
-      <c r="D4" s="30" t="s">
+      <c r="D4" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="E4" s="30" t="s">
+      <c r="E4" s="24" t="s">
         <v>135</v>
       </c>
-      <c r="F4" s="30" t="s">
+      <c r="F4" s="24" t="s">
         <v>122</v>
       </c>
-      <c r="G4" s="30"/>
-      <c r="H4" s="30" t="s">
+      <c r="G4" s="24"/>
+      <c r="H4" s="24" t="s">
         <v>123</v>
       </c>
-      <c r="I4" s="30">
+      <c r="I4" s="24">
         <v>5</v>
       </c>
-      <c r="J4" s="30" t="s">
+      <c r="J4" s="24" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="49.2">
+    <row r="5" spans="1:10" ht="86.4">
       <c r="A5" s="6">
         <v>4</v>
       </c>
-      <c r="B5" s="30" t="s">
+      <c r="B5" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="C5" s="30" t="s">
+      <c r="C5" s="24" t="s">
         <v>124</v>
       </c>
-      <c r="D5" s="30" t="s">
+      <c r="D5" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="E5" s="30" t="s">
+      <c r="E5" s="24" t="s">
         <v>137</v>
       </c>
-      <c r="F5" s="30" t="s">
+      <c r="F5" s="24" t="s">
         <v>138</v>
       </c>
-      <c r="G5" s="30"/>
-      <c r="H5" s="30" t="s">
+      <c r="G5" s="31" t="s">
+        <v>140</v>
+      </c>
+      <c r="H5" s="24" t="s">
         <v>125</v>
       </c>
-      <c r="I5" s="30">
+      <c r="I5" s="24">
         <v>4</v>
       </c>
-      <c r="J5" s="30" t="s">
+      <c r="J5" s="24" t="s">
         <v>126</v>
       </c>
     </row>
@@ -2149,33 +2157,36 @@
       <c r="A6" s="6">
         <v>5</v>
       </c>
-      <c r="B6" s="30" t="s">
+      <c r="B6" s="24" t="s">
         <v>127</v>
       </c>
-      <c r="C6" s="30" t="s">
+      <c r="C6" s="24" t="s">
         <v>128</v>
       </c>
-      <c r="D6" s="30" t="s">
+      <c r="D6" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="E6" s="30" t="s">
+      <c r="E6" s="24" t="s">
         <v>139</v>
       </c>
-      <c r="F6" s="30" t="s">
+      <c r="F6" s="24" t="s">
         <v>129</v>
       </c>
-      <c r="G6" s="30"/>
-      <c r="H6" s="30" t="s">
+      <c r="G6" s="24"/>
+      <c r="H6" s="24" t="s">
         <v>130</v>
       </c>
-      <c r="I6" s="30">
+      <c r="I6" s="24">
         <v>5</v>
       </c>
-      <c r="J6" s="30" t="s">
+      <c r="J6" s="24" t="s">
         <v>131</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="G5" r:id="rId1" xr:uid="{F78440F2-16AB-4755-84EF-B90E0136DE2A}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/Template_PRJ301_AI_Usage_Report_Template (1) (2).xlsx
+++ b/docs/Template_PRJ301_AI_Usage_Report_Template (1) (2).xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="148">
   <si>
     <t>PRJ301 - Project AI Usage Report</t>
   </si>
@@ -350,6 +350,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t>Provided the </t>
     </r>
     <r>
@@ -371,6 +376,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t>Verified the connection string, adjusted the database name to </t>
     </r>
     <r>
@@ -407,6 +417,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t>Generated standard Servlet structure (</t>
     </r>
     <r>
@@ -460,6 +475,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t>Reviewed the Servlet code, customized the URL patterns (e.g., </t>
     </r>
     <r>
@@ -503,6 +523,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t>AI used deprecated imports (</t>
     </r>
     <r>
@@ -546,6 +571,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t>Wrote SQL queries using </t>
     </r>
     <r>
@@ -592,6 +622,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t>AI code lacked specific error handling for foreign key constraints; manually added </t>
     </r>
     <r>
@@ -616,6 +651,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t>Provided </t>
     </r>
     <r>
@@ -653,6 +693,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t>Applied the Filter to sensitive routes (</t>
     </r>
     <r>
@@ -721,6 +766,9 @@
     </r>
   </si>
   <si>
+    <t>https://drive.google.com/drive/folders/1HDAnlKy5GQiDcsJ5ka-zU_YZRkGuqeTY?usp=sharing</t>
+  </si>
+  <si>
     <t>1 Filter class and 2 updated JSP files</t>
   </si>
   <si>
@@ -734,6 +782,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t>Suggested </t>
     </r>
     <r>
@@ -846,7 +899,7 @@
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_-* #,##0\ &quot;₫&quot;_-;\-* #,##0\ &quot;₫&quot;_-;_-* &quot;-&quot;\ &quot;₫&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -897,13 +950,6 @@
       <color theme="1"/>
       <name val="Times New Roman"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -1055,11 +1101,6 @@
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Times New Roman"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="37">
@@ -1459,130 +1500,130 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1630,16 +1671,16 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="6" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="6" applyAlignment="1">
@@ -1654,10 +1695,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="6" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2739,7 +2780,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="5" ht="55.2" spans="1:10">
+    <row r="5" ht="86.4" spans="1:10">
       <c r="A5" s="10">
         <v>4</v>
       </c>
@@ -2758,15 +2799,17 @@
       <c r="F5" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="G5" s="8"/>
+      <c r="G5" s="9" t="s">
+        <v>126</v>
+      </c>
       <c r="H5" s="8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I5" s="8">
         <v>4</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="6" ht="82.8" spans="1:10">
@@ -2774,31 +2817,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>26</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I6" s="8">
         <v>5</v>
       </c>
       <c r="J6" s="8" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>
@@ -2807,6 +2850,7 @@
     <hyperlink ref="G3" r:id="rId2" display="https://drive.google.com/drive/folders/1mkeoPv7QBeEjPVionr3T6jgvSR-VMuW3?usp=sharing"/>
     <hyperlink ref="G6" r:id="rId3" display="https://drive.google.com/drive/folders/18528q5unPQgaTq-89bPzC0Es6qiiTV2f?usp=sharing"/>
     <hyperlink ref="G4" r:id="rId4" display="https://drive.google.com/drive/folders/1BT8UQCi9wl8cJyHOPO71V5_QBshXmKtW?usp=sharing"/>
+    <hyperlink ref="G5" r:id="rId5" display="https://drive.google.com/drive/folders/1HDAnlKy5GQiDcsJ5ka-zU_YZRkGuqeTY?usp=sharing"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -2825,10 +2869,10 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -2836,7 +2880,7 @@
         <v>36</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="3" ht="26.4" spans="1:2">
@@ -2844,7 +2888,7 @@
         <v>37</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="4" ht="26.4" spans="1:2">
@@ -2852,7 +2896,7 @@
         <v>38</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -2860,7 +2904,7 @@
         <v>39</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="6" ht="26.4" spans="1:2">
@@ -2868,7 +2912,7 @@
         <v>40</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="7" ht="26.4" spans="1:2">
@@ -2876,7 +2920,7 @@
         <v>41</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="8" ht="39.6" spans="1:2">
@@ -2884,7 +2928,7 @@
         <v>42</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="9" ht="26.4" spans="1:2">
@@ -2892,7 +2936,7 @@
         <v>43</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -2900,7 +2944,7 @@
         <v>44</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11" ht="26.4" spans="1:2">
@@ -2908,7 +2952,7 @@
         <v>45</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
   </sheetData>
